--- a/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultatiRandom_CONF1_RUN_4.xlsx
+++ b/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultatiRandom_CONF1_RUN_4.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="150" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="295" uniqueCount="22">
   <si>
     <t>Scenario</t>
   </si>
@@ -153,19 +153,19 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" s="0">
-        <v>30.055009820698551</v>
+        <v>2.4264451165355911</v>
       </c>
       <c r="D2" s="0" t="b">
         <v>0</v>
       </c>
       <c r="E2" s="0">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -173,10 +173,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="0">
-        <v>-5.0415136891137564</v>
+        <v>-5.0054774643551463</v>
       </c>
       <c r="D3" s="0" t="b">
         <v>1</v>
@@ -185,31 +185,31 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" s="0">
-        <v>2.207484371593992</v>
+        <v>-5.221722509689517</v>
       </c>
       <c r="D4" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="0"/>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" s="0">
-        <v>-5.3978966294493445</v>
+        <v>30.055009820698551</v>
       </c>
       <c r="D5" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="0"/>
     </row>
@@ -218,10 +218,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="0">
-        <v>3.5491290917359901</v>
+        <v>0.70527010787779609</v>
       </c>
       <c r="D6" s="0" t="b">
         <v>0</v>
@@ -230,13 +230,13 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C7" s="0">
-        <v>-4.8224758114685278</v>
+        <v>-4.8863300664008902</v>
       </c>
       <c r="D7" s="0" t="b">
         <v>1</v>
@@ -245,43 +245,43 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8" s="0">
-        <v>30.174186611542254</v>
+        <v>-5.0485200940389836</v>
       </c>
       <c r="D8" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="0"/>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C9" s="0">
-        <v>-4.8425262762849748</v>
+        <v>21.097326422705773</v>
       </c>
       <c r="D9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0"/>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="0">
-        <v>19.121179507586412</v>
+        <v>6.1897486482633077</v>
       </c>
       <c r="D10" s="0" t="b">
         <v>0</v>
@@ -290,13 +290,13 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11" s="0">
-        <v>-4.8863300664008902</v>
+        <v>-4.8815706647960955</v>
       </c>
       <c r="D11" s="0" t="b">
         <v>1</v>
@@ -308,10 +308,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C12" s="0">
-        <v>29.592585200397785</v>
+        <v>29.948238707703801</v>
       </c>
       <c r="D12" s="0" t="b">
         <v>0</v>
@@ -320,13 +320,13 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C13" s="0">
-        <v>24.786647501715848</v>
+        <v>20.168556842943516</v>
       </c>
       <c r="D13" s="0" t="b">
         <v>0</v>
@@ -335,43 +335,43 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" s="0">
-        <v>6.1897486482633077</v>
+        <v>-5.4450041779474443</v>
       </c>
       <c r="D14" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="0"/>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="0">
-        <v>1.9506559854166206</v>
+        <v>-4.8425262762849748</v>
       </c>
       <c r="D15" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="0"/>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="0">
-        <v>0.70527010787779609</v>
+        <v>5.3560234068479318</v>
       </c>
       <c r="D16" s="0" t="b">
         <v>0</v>
@@ -380,43 +380,43 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" s="0">
-        <v>-4.9637324106799197</v>
+        <v>22.440207133110825</v>
       </c>
       <c r="D17" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="0"/>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>13</v>
       </c>
       <c r="C18" s="0">
-        <v>-5.8039810306779049</v>
+        <v>2.207484371593992</v>
       </c>
       <c r="D18" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="0"/>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C19" s="0">
-        <v>2.4264451165355911</v>
+        <v>37.105685164052545</v>
       </c>
       <c r="D19" s="0" t="b">
         <v>0</v>
@@ -425,16 +425,16 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" s="0">
-        <v>5.3560234068479318</v>
+        <v>-5.3978966294493445</v>
       </c>
       <c r="D20" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="0"/>
     </row>
@@ -443,10 +443,10 @@
         <v>3</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C21" s="0">
-        <v>25.882739787688216</v>
+        <v>25.699545964216526</v>
       </c>
       <c r="D21" s="0" t="b">
         <v>0</v>
@@ -470,13 +470,13 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C23" s="0">
-        <v>38.515121907499733</v>
+        <v>19.913981501717963</v>
       </c>
       <c r="D23" s="0" t="b">
         <v>0</v>
@@ -485,16 +485,16 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C24" s="0">
-        <v>-5.3676771425456309</v>
+        <v>38.224737862406691</v>
       </c>
       <c r="D24" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="0"/>
     </row>
@@ -503,10 +503,10 @@
         <v>10</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C25" s="0">
-        <v>21.097326422705773</v>
+        <v>19.551260111276569</v>
       </c>
       <c r="D25" s="0" t="b">
         <v>0</v>
@@ -515,13 +515,13 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C26" s="0">
-        <v>38.52506278830694</v>
+        <v>25.882739787688216</v>
       </c>
       <c r="D26" s="0" t="b">
         <v>0</v>
@@ -530,43 +530,43 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C27" s="0">
-        <v>19.551260111276569</v>
+        <v>-4.9132709455110097</v>
       </c>
       <c r="D27" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="0"/>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" s="0">
-        <v>-5.4450041779474443</v>
+        <v>24.786647501715848</v>
       </c>
       <c r="D28" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="0"/>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" s="0">
-        <v>23.343334587647796</v>
+        <v>25.318079812350447</v>
       </c>
       <c r="D29" s="0" t="b">
         <v>0</v>
@@ -575,28 +575,28 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C30" s="0">
-        <v>-4.9976510102555673</v>
+        <v>30.174186611542254</v>
       </c>
       <c r="D30" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="0"/>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C31" s="0">
-        <v>38.224737862406691</v>
+        <v>1.2624213627403336</v>
       </c>
       <c r="D31" s="0" t="b">
         <v>0</v>
@@ -605,13 +605,13 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C32" s="0">
-        <v>3.090034130685293</v>
+        <v>1.9506559854166206</v>
       </c>
       <c r="D32" s="0" t="b">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>8</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="0">
-        <v>5.8437784426107573</v>
+        <v>3.1518026589919899</v>
       </c>
       <c r="D33" s="0" t="b">
         <v>0</v>
@@ -635,28 +635,28 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C34" s="0">
-        <v>26.096080886783085</v>
+        <v>-4.9637324106799197</v>
       </c>
       <c r="D34" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="0"/>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="0">
-        <v>16.179942240403751</v>
+        <v>24.063587591923785</v>
       </c>
       <c r="D35" s="0" t="b">
         <v>0</v>
@@ -665,145 +665,193 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="0">
+        <v>-4.8875972816218454</v>
+      </c>
+      <c r="D36" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="0"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="0">
+        <v>-4.8224758114685278</v>
+      </c>
+      <c r="D37" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="0"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="0">
+        <v>19.775888433823287</v>
+      </c>
+      <c r="D38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" s="0"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="0">
+        <v>26.096080886783085</v>
+      </c>
+      <c r="D39" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="0"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="0">
+        <v>21.209269994395491</v>
+      </c>
+      <c r="D40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" s="0"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="0">
+        <v>38.515121907499733</v>
+      </c>
+      <c r="D41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="0"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="0">
+        <v>29.91667766430195</v>
+      </c>
+      <c r="D42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="0"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="0">
+        <v>-5.0023402002739914</v>
+      </c>
+      <c r="D43" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="0"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="0">
+        <v>-5.8039810306779049</v>
+      </c>
+      <c r="D44" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="0"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="0">
+        <v>-5.1155456861083568</v>
+      </c>
+      <c r="D45" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="0"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="0">
+        <v>-4.9305520454120613</v>
+      </c>
+      <c r="D46" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="0"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B47" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="0">
+      <c r="C47" s="0">
         <v>3.2649773528189563</v>
       </c>
-      <c r="D36" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" s="0"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="0"/>
-      <c r="B37" s="0"/>
-      <c r="C37" s="0">
-        <v>0</v>
-      </c>
-      <c r="D37" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" s="0"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="0"/>
-      <c r="B38" s="0"/>
-      <c r="C38" s="0">
-        <v>0</v>
-      </c>
-      <c r="D38" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" s="0"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="0"/>
-      <c r="B39" s="0"/>
-      <c r="C39" s="0">
-        <v>0</v>
-      </c>
-      <c r="D39" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" s="0"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="0"/>
-      <c r="B40" s="0"/>
-      <c r="C40" s="0">
-        <v>0</v>
-      </c>
-      <c r="D40" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" s="0"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="0"/>
-      <c r="B41" s="0"/>
-      <c r="C41" s="0">
-        <v>0</v>
-      </c>
-      <c r="D41" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="E41" s="0"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="0"/>
-      <c r="B42" s="0"/>
-      <c r="C42" s="0">
-        <v>0</v>
-      </c>
-      <c r="D42" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" s="0"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="0"/>
-      <c r="B43" s="0"/>
-      <c r="C43" s="0">
-        <v>0</v>
-      </c>
-      <c r="D43" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="E43" s="0"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="0"/>
-      <c r="B44" s="0"/>
-      <c r="C44" s="0">
-        <v>0</v>
-      </c>
-      <c r="D44" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="E44" s="0"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="0"/>
-      <c r="B45" s="0"/>
-      <c r="C45" s="0">
-        <v>0</v>
-      </c>
-      <c r="D45" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" s="0"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="0"/>
-      <c r="B46" s="0"/>
-      <c r="C46" s="0">
-        <v>0</v>
-      </c>
-      <c r="D46" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" s="0"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="0"/>
-      <c r="B47" s="0"/>
-      <c r="C47" s="0">
-        <v>0</v>
-      </c>
       <c r="D47" s="0" t="b">
         <v>0</v>
       </c>
       <c r="E47" s="0"/>
     </row>
     <row r="48">
-      <c r="A48" s="0"/>
-      <c r="B48" s="0"/>
+      <c r="A48" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>18</v>
+      </c>
       <c r="C48" s="0">
-        <v>0</v>
+        <v>5.7924153506839602</v>
       </c>
       <c r="D48" s="0" t="b">
         <v>0</v>
@@ -811,10 +859,14 @@
       <c r="E48" s="0"/>
     </row>
     <row r="49">
-      <c r="A49" s="0"/>
-      <c r="B49" s="0"/>
+      <c r="A49" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>18</v>
+      </c>
       <c r="C49" s="0">
-        <v>0</v>
+        <v>28.874252804143765</v>
       </c>
       <c r="D49" s="0" t="b">
         <v>0</v>
@@ -822,10 +874,14 @@
       <c r="E49" s="0"/>
     </row>
     <row r="50">
-      <c r="A50" s="0"/>
-      <c r="B50" s="0"/>
+      <c r="A50" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>12</v>
+      </c>
       <c r="C50" s="0">
-        <v>0</v>
+        <v>29.592585200397785</v>
       </c>
       <c r="D50" s="0" t="b">
         <v>0</v>
@@ -833,21 +889,29 @@
       <c r="E50" s="0"/>
     </row>
     <row r="51">
-      <c r="A51" s="0"/>
-      <c r="B51" s="0"/>
+      <c r="A51" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>15</v>
+      </c>
       <c r="C51" s="0">
-        <v>0</v>
+        <v>-4.917282062953845</v>
       </c>
       <c r="D51" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="0"/>
     </row>
     <row r="52">
-      <c r="A52" s="0"/>
-      <c r="B52" s="0"/>
+      <c r="A52" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>13</v>
+      </c>
       <c r="C52" s="0">
-        <v>0</v>
+        <v>37.094292868652857</v>
       </c>
       <c r="D52" s="0" t="b">
         <v>0</v>
@@ -855,10 +919,14 @@
       <c r="E52" s="0"/>
     </row>
     <row r="53">
-      <c r="A53" s="0"/>
-      <c r="B53" s="0"/>
+      <c r="A53" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>15</v>
+      </c>
       <c r="C53" s="0">
-        <v>0</v>
+        <v>16.179942240403751</v>
       </c>
       <c r="D53" s="0" t="b">
         <v>0</v>
@@ -866,10 +934,14 @@
       <c r="E53" s="0"/>
     </row>
     <row r="54">
-      <c r="A54" s="0"/>
-      <c r="B54" s="0"/>
+      <c r="A54" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>17</v>
+      </c>
       <c r="C54" s="0">
-        <v>0</v>
+        <v>38.52506278830694</v>
       </c>
       <c r="D54" s="0" t="b">
         <v>0</v>
@@ -877,10 +949,14 @@
       <c r="E54" s="0"/>
     </row>
     <row r="55">
-      <c r="A55" s="0"/>
-      <c r="B55" s="0"/>
+      <c r="A55" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>12</v>
+      </c>
       <c r="C55" s="0">
-        <v>0</v>
+        <v>24.10042054542923</v>
       </c>
       <c r="D55" s="0" t="b">
         <v>0</v>
@@ -888,10 +964,14 @@
       <c r="E55" s="0"/>
     </row>
     <row r="56">
-      <c r="A56" s="0"/>
-      <c r="B56" s="0"/>
+      <c r="A56" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>16</v>
+      </c>
       <c r="C56" s="0">
-        <v>0</v>
+        <v>19.121179507586412</v>
       </c>
       <c r="D56" s="0" t="b">
         <v>0</v>
@@ -899,32 +979,44 @@
       <c r="E56" s="0"/>
     </row>
     <row r="57">
-      <c r="A57" s="0"/>
-      <c r="B57" s="0"/>
+      <c r="A57" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>13</v>
+      </c>
       <c r="C57" s="0">
-        <v>0</v>
+        <v>-5.0415136891137564</v>
       </c>
       <c r="D57" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="0"/>
     </row>
     <row r="58">
-      <c r="A58" s="0"/>
-      <c r="B58" s="0"/>
+      <c r="A58" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>18</v>
+      </c>
       <c r="C58" s="0">
-        <v>0</v>
+        <v>-4.9976510102555673</v>
       </c>
       <c r="D58" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="0"/>
     </row>
     <row r="59">
-      <c r="A59" s="0"/>
-      <c r="B59" s="0"/>
+      <c r="A59" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>15</v>
+      </c>
       <c r="C59" s="0">
-        <v>0</v>
+        <v>-5.7460253769178946</v>
       </c>
       <c r="D59" s="0" t="b">
         <v>0</v>
@@ -932,10 +1024,14 @@
       <c r="E59" s="0"/>
     </row>
     <row r="60">
-      <c r="A60" s="0"/>
-      <c r="B60" s="0"/>
+      <c r="A60" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>14</v>
+      </c>
       <c r="C60" s="0">
-        <v>0</v>
+        <v>3.090034130685293</v>
       </c>
       <c r="D60" s="0" t="b">
         <v>0</v>
@@ -943,10 +1039,14 @@
       <c r="E60" s="0"/>
     </row>
     <row r="61">
-      <c r="A61" s="0"/>
-      <c r="B61" s="0"/>
+      <c r="A61" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>13</v>
+      </c>
       <c r="C61" s="0">
-        <v>0</v>
+        <v>1.4772436234657196</v>
       </c>
       <c r="D61" s="0" t="b">
         <v>0</v>
@@ -954,21 +1054,29 @@
       <c r="E61" s="0"/>
     </row>
     <row r="62">
-      <c r="A62" s="0"/>
-      <c r="B62" s="0"/>
+      <c r="A62" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>14</v>
+      </c>
       <c r="C62" s="0">
-        <v>0</v>
+        <v>-5.0595316519657541</v>
       </c>
       <c r="D62" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="0"/>
     </row>
     <row r="63">
-      <c r="A63" s="0"/>
-      <c r="B63" s="0"/>
+      <c r="A63" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>14</v>
+      </c>
       <c r="C63" s="0">
-        <v>0</v>
+        <v>6.1526096058418496</v>
       </c>
       <c r="D63" s="0" t="b">
         <v>0</v>
@@ -976,21 +1084,29 @@
       <c r="E63" s="0"/>
     </row>
     <row r="64">
-      <c r="A64" s="0"/>
-      <c r="B64" s="0"/>
+      <c r="A64" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>13</v>
+      </c>
       <c r="C64" s="0">
-        <v>0</v>
+        <v>-5.3676771425456309</v>
       </c>
       <c r="D64" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" s="0"/>
     </row>
     <row r="65">
-      <c r="A65" s="0"/>
-      <c r="B65" s="0"/>
+      <c r="A65" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>18</v>
+      </c>
       <c r="C65" s="0">
-        <v>0</v>
+        <v>38.652954511366083</v>
       </c>
       <c r="D65" s="0" t="b">
         <v>0</v>
@@ -998,10 +1114,14 @@
       <c r="E65" s="0"/>
     </row>
     <row r="66">
-      <c r="A66" s="0"/>
-      <c r="B66" s="0"/>
+      <c r="A66" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>14</v>
+      </c>
       <c r="C66" s="0">
-        <v>0</v>
+        <v>23.343334587647796</v>
       </c>
       <c r="D66" s="0" t="b">
         <v>0</v>
@@ -1009,10 +1129,14 @@
       <c r="E66" s="0"/>
     </row>
     <row r="67">
-      <c r="A67" s="0"/>
-      <c r="B67" s="0"/>
+      <c r="A67" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>12</v>
+      </c>
       <c r="C67" s="0">
-        <v>0</v>
+        <v>5.8437784426107573</v>
       </c>
       <c r="D67" s="0" t="b">
         <v>0</v>
@@ -1020,10 +1144,14 @@
       <c r="E67" s="0"/>
     </row>
     <row r="68">
-      <c r="A68" s="0"/>
-      <c r="B68" s="0"/>
+      <c r="A68" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>17</v>
+      </c>
       <c r="C68" s="0">
-        <v>0</v>
+        <v>3.5491290917359901</v>
       </c>
       <c r="D68" s="0" t="b">
         <v>0</v>
@@ -1031,10 +1159,14 @@
       <c r="E68" s="0"/>
     </row>
     <row r="69">
-      <c r="A69" s="0"/>
-      <c r="B69" s="0"/>
+      <c r="A69" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>18</v>
+      </c>
       <c r="C69" s="0">
-        <v>0</v>
+        <v>16.262995389481183</v>
       </c>
       <c r="D69" s="0" t="b">
         <v>0</v>
@@ -1042,10 +1174,14 @@
       <c r="E69" s="0"/>
     </row>
     <row r="70">
-      <c r="A70" s="0"/>
-      <c r="B70" s="0"/>
+      <c r="A70" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>14</v>
+      </c>
       <c r="C70" s="0">
-        <v>0</v>
+        <v>38.413814022374339</v>
       </c>
       <c r="D70" s="0" t="b">
         <v>0</v>
@@ -1053,10 +1189,14 @@
       <c r="E70" s="0"/>
     </row>
     <row r="71">
-      <c r="A71" s="0"/>
-      <c r="B71" s="0"/>
+      <c r="A71" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>18</v>
+      </c>
       <c r="C71" s="0">
-        <v>0</v>
+        <v>25.331878621854834</v>
       </c>
       <c r="D71" s="0" t="b">
         <v>0</v>
